--- a/examples/excel/charts/charts-boxwhisker.xlsx
+++ b/examples/excel/charts/charts-boxwhisker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Basics &amp; Quartile" sheetId="2" r:id="Rf393d9ca8a6246ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Axes &amp; Styling" sheetId="3" r:id="Ra872b54dc8ba4364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Basics &amp; Quartile" sheetId="2" r:id="R3b40ca46bc184339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Axes &amp; Styling" sheetId="3" r:id="R9ef6650a7bdf489a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra0e3af32478f4b40"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R33a2da6fccc444c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -64,7 +64,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rd88cb88f543b4ad6"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R368195fa13724721"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -94,7 +94,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re147d554980143c2"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Recb70e81afe347fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -124,7 +124,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R972687f1934b4d69"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1831e29045b043f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -159,7 +159,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re728d8330ee343d6"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R7212500ffa1f44be"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -189,7 +189,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R19dcd860399648ef"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R2222f36f3ec545de"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -219,7 +219,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0c4a29de97414876"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3949504b61b44072"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -249,7 +249,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4abba7b7b72b4acc"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1fa3422874c44dd7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -259,10 +259,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$18</cx:f>
         <cx:lvl ptCount="17">
           <cx:pt idx="0">Scores</cx:pt>
           <cx:pt idx="1">Scores</cx:pt>
@@ -284,6 +285,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$18</cx:f>
         <cx:lvl ptCount="17" formatCode="General">
           <cx:pt idx="0">45</cx:pt>
           <cx:pt idx="1">52</cx:pt>
@@ -310,8 +312,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Test Score Distribution</a:t>
@@ -322,14 +324,14 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{48E7EAA5-17C6-48B1-BC62-04FAB68DDBD1}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
               <cx:v>Scores</cx:v>
             </cx:txData>
           </cx:tx>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -354,10 +356,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">Engineering</cx:pt>
           <cx:pt idx="1">Engineering</cx:pt>
@@ -375,6 +378,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">85</cx:pt>
           <cx:pt idx="1">92</cx:pt>
@@ -394,6 +398,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$C$2:$C$13</cx:f>
         <cx:lvl ptCount="12">
           <cx:pt idx="0">Marketing</cx:pt>
           <cx:pt idx="1">Marketing</cx:pt>
@@ -410,6 +415,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$C$2:$C$13</cx:f>
         <cx:lvl ptCount="12" formatCode="General">
           <cx:pt idx="0">60</cx:pt>
           <cx:pt idx="1">65</cx:pt>
@@ -428,6 +434,7 @@
     </cx:data>
     <cx:data id="2">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$D$2:$D$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">Sales</cx:pt>
           <cx:pt idx="1">Sales</cx:pt>
@@ -445,6 +452,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$D$2:$D$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">55</cx:pt>
           <cx:pt idx="1">62</cx:pt>
@@ -467,8 +475,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Salary by Department ($k)</a:t>
@@ -479,10 +487,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{A1AC5EC2-9457-4CCF-B4F5-B7BB35C191C9}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
               <cx:v>Engineering</cx:v>
             </cx:txData>
           </cx:tx>
@@ -492,10 +500,10 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{6A16FC0A-CD83-47C5-BBC0-EC2653902AB4}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$C$1</cx:f>
               <cx:v>Marketing</cx:v>
             </cx:txData>
           </cx:tx>
@@ -505,10 +513,10 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{DF161513-1CBE-4D67-B86E-9757ABFD8700}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$D$1</cx:f>
               <cx:v>Sales</cx:v>
             </cx:txData>
           </cx:tx>
@@ -535,10 +543,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$15</cx:f>
         <cx:lvl ptCount="14">
           <cx:pt idx="0">Data</cx:pt>
           <cx:pt idx="1">Data</cx:pt>
@@ -557,6 +566,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$15</cx:f>
         <cx:lvl ptCount="14" formatCode="General">
           <cx:pt idx="0">18</cx:pt>
           <cx:pt idx="1">22</cx:pt>
@@ -580,8 +590,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US" sz="2000" b="1">
                 <a:solidFill>
@@ -605,10 +615,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{7F66C1B3-7761-414D-BD0A-34098D6C7DAA}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
               <cx:v>Data</cx:v>
             </cx:txData>
           </cx:tx>
@@ -634,10 +644,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">GroupA</cx:pt>
           <cx:pt idx="1">GroupA</cx:pt>
@@ -655,6 +666,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">30</cx:pt>
           <cx:pt idx="1">38</cx:pt>
@@ -674,6 +686,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
+        <cx:f>1-Basics &amp; Quartile!$C$2:$C$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">GroupB</cx:pt>
           <cx:pt idx="1">GroupB</cx:pt>
@@ -691,6 +704,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>1-Basics &amp; Quartile!$C$2:$C$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">20</cx:pt>
           <cx:pt idx="1">28</cx:pt>
@@ -713,8 +727,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Custom Series Colors</a:t>
@@ -725,18 +739,18 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{1B414184-D429-4404-8DE9-46CF00651883}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
               <cx:v>GroupA</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="5B9BD5"/>
             </a:solidFill>
-            <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:effectLst>
               <a:outerShdw blurRad="76200" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
                   <a:alpha val="35000"/>
@@ -750,18 +764,18 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{3EC803A6-9C8C-4A66-A2BB-2B8211B49455}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>1-Basics &amp; Quartile!$C$1</cx:f>
               <cx:v>GroupB</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="ED7D31"/>
             </a:solidFill>
-            <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:effectLst>
               <a:outerShdw blurRad="76200" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
                   <a:alpha val="35000"/>
@@ -791,10 +805,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$18</cx:f>
         <cx:lvl ptCount="17">
           <cx:pt idx="0">API</cx:pt>
           <cx:pt idx="1">API</cx:pt>
@@ -816,6 +831,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$18</cx:f>
         <cx:lvl ptCount="17" formatCode="General">
           <cx:pt idx="0">12</cx:pt>
           <cx:pt idx="1">18</cx:pt>
@@ -839,6 +855,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$C$2:$C$16</cx:f>
         <cx:lvl ptCount="15">
           <cx:pt idx="0">DB</cx:pt>
           <cx:pt idx="1">DB</cx:pt>
@@ -858,6 +875,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$C$2:$C$16</cx:f>
         <cx:lvl ptCount="15" formatCode="General">
           <cx:pt idx="0">5</cx:pt>
           <cx:pt idx="1">8</cx:pt>
@@ -882,8 +900,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Response Time (ms)</a:t>
@@ -894,10 +912,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{3D480C6F-2E0A-470C-BCFD-50AA5ABC1001}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
               <cx:v>API</cx:v>
             </cx:txData>
           </cx:tx>
@@ -907,10 +925,10 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{6127D534-374C-4E9D-8966-20648B6FD639}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$C$1</cx:f>
               <cx:v>DB</cx:v>
             </cx:txData>
           </cx:tx>
@@ -926,8 +944,8 @@
         <cx:title>
           <cx:tx>
             <cx:rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:r>
                   <a:rPr lang="en-US" sz="1200" b="1">
                     <a:solidFill>
@@ -944,9 +962,9 @@
         </cx:title>
         <cx:tickLabels/>
         <cx:txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000">
                 <a:solidFill>
@@ -964,8 +982,8 @@
         <cx:title>
           <cx:tx>
             <cx:rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:r>
                   <a:rPr lang="en-US" sz="1200" b="1">
                     <a:solidFill>
@@ -983,9 +1001,9 @@
         <cx:majorGridlines/>
         <cx:tickLabels/>
         <cx:txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000">
                 <a:solidFill>
@@ -1004,10 +1022,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13">
           <cx:pt idx="0">Temp</cx:pt>
           <cx:pt idx="1">Temp</cx:pt>
@@ -1025,6 +1044,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$14</cx:f>
         <cx:lvl ptCount="13" formatCode="General">
           <cx:pt idx="0">15</cx:pt>
           <cx:pt idx="1">18</cx:pt>
@@ -1047,8 +1067,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Axis &amp; Gridline Control</a:t>
@@ -1059,10 +1079,10 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{DF75A714-5514-4DB6-B1F6-CA468B47E88D}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
               <cx:v>Temp</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1077,7 +1097,7 @@
         <cx:catScaling/>
         <cx:majorGridlines>
           <cx:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="F1F5F9"/>
               </a:solidFill>
@@ -1090,7 +1110,7 @@
         <cx:valScaling/>
         <cx:majorGridlines>
           <cx:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="E2E8F0"/>
               </a:solidFill>
@@ -1099,7 +1119,7 @@
         </cx:majorGridlines>
         <cx:tickLabels/>
         <cx:spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+          <a:ln w="19050">
             <a:solidFill>
               <a:srgbClr val="334155"/>
             </a:solidFill>
@@ -1112,10 +1132,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$16</cx:f>
         <cx:lvl ptCount="15">
           <cx:pt idx="0">Weight</cx:pt>
           <cx:pt idx="1">Weight</cx:pt>
@@ -1135,6 +1156,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$16</cx:f>
         <cx:lvl ptCount="15" formatCode="General">
           <cx:pt idx="0">50</cx:pt>
           <cx:pt idx="1">55</cx:pt>
@@ -1159,8 +1181,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US"/>
               <a:t>Card Style</a:t>
@@ -1171,15 +1193,15 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{592CB1B6-9BCC-4F87-A3A5-6BF299FEA71F}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
               <cx:v>Weight</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="6366F1"/>
             </a:solidFill>
           </cx:spPr>
@@ -1197,10 +1219,10 @@
         <cx:valScaling/>
       </cx:axis>
       <cx:spPr>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:solidFill>
           <a:srgbClr val="F8FAFC"/>
         </a:solidFill>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="E2E8F0"/>
           </a:solidFill>
@@ -1209,10 +1231,10 @@
     </cx:plotArea>
   </cx:chart>
   <cx:spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+    <a:ln w="9525">
       <a:solidFill>
         <a:srgbClr val="CBD5E1"/>
       </a:solidFill>
@@ -1222,10 +1244,11 @@
 </file>
 
 <file path=xl/drawings/extendedCharts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$16</cx:f>
         <cx:lvl ptCount="15">
           <cx:pt idx="0">US-East</cx:pt>
           <cx:pt idx="1">US-East</cx:pt>
@@ -1245,6 +1268,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$B$2:$B$16</cx:f>
         <cx:lvl ptCount="15" formatCode="General">
           <cx:pt idx="0">8</cx:pt>
           <cx:pt idx="1">12</cx:pt>
@@ -1266,6 +1290,7 @@
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$C$2:$C$15</cx:f>
         <cx:lvl ptCount="14">
           <cx:pt idx="0">EU-West</cx:pt>
           <cx:pt idx="1">EU-West</cx:pt>
@@ -1284,6 +1309,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$C$2:$C$15</cx:f>
         <cx:lvl ptCount="14" formatCode="General">
           <cx:pt idx="0">10</cx:pt>
           <cx:pt idx="1">14</cx:pt>
@@ -1304,6 +1330,7 @@
     </cx:data>
     <cx:data id="2">
       <cx:strDim type="cat">
+        <cx:f>2-Axes &amp; Styling!$D$2:$D$16</cx:f>
         <cx:lvl ptCount="15">
           <cx:pt idx="0">AP-South</cx:pt>
           <cx:pt idx="1">AP-South</cx:pt>
@@ -1323,6 +1350,7 @@
         </cx:lvl>
       </cx:strDim>
       <cx:numDim type="val">
+        <cx:f>2-Axes &amp; Styling!$D$2:$D$16</cx:f>
         <cx:lvl ptCount="15" formatCode="General">
           <cx:pt idx="0">15</cx:pt>
           <cx:pt idx="1">20</cx:pt>
@@ -1347,8 +1375,8 @@
     <cx:title>
       <cx:tx>
         <cx:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:r>
               <a:rPr lang="en-US" sz="1800" b="1">
                 <a:solidFill>
@@ -1372,18 +1400,18 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{19921A0A-F210-4308-95D4-733129E3E8B4}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
               <cx:v>US-East</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="3B82F6"/>
             </a:solidFill>
-            <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:effectLst>
               <a:outerShdw blurRad="50800" dist="25400" dir="2700000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
                   <a:alpha val="30000"/>
@@ -1391,7 +1419,7 @@
               </a:outerShdw>
             </a:effectLst>
           </cx:spPr>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:numFmt formatCode="0" sourceLinked="0"/>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
@@ -1401,18 +1429,18 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{784E9993-1C87-4058-9638-D446F8C45504}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$C$1</cx:f>
               <cx:v>EU-West</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="10B981"/>
             </a:solidFill>
-            <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:effectLst>
               <a:outerShdw blurRad="50800" dist="25400" dir="2700000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
                   <a:alpha val="30000"/>
@@ -1420,7 +1448,7 @@
               </a:outerShdw>
             </a:effectLst>
           </cx:spPr>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:numFmt formatCode="0" sourceLinked="0"/>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
@@ -1430,18 +1458,18 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker">
+        <cx:series layoutId="boxWhisker" uniqueId="{AB5C43A4-4EFA-4100-A150-D0DDBC97BA30}">
           <cx:tx>
             <cx:txData>
-              <cx:f/>
+              <cx:f>2-Axes &amp; Styling!$D$1</cx:f>
               <cx:v>AP-South</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="F59E0B"/>
             </a:solidFill>
-            <a:effectLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:effectLst>
               <a:outerShdw blurRad="50800" dist="25400" dir="2700000" algn="tl" rotWithShape="0">
                 <a:srgbClr val="000000">
                   <a:alpha val="30000"/>
@@ -1449,7 +1477,7 @@
               </a:outerShdw>
             </a:effectLst>
           </cx:spPr>
-          <cx:dataLabels pos="outEnd">
+          <cx:dataLabels>
             <cx:numFmt formatCode="0" sourceLinked="0"/>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
@@ -1465,8 +1493,8 @@
         <cx:title>
           <cx:tx>
             <cx:rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:r>
                   <a:rPr lang="en-US" sz="1100" b="1">
                     <a:solidFill>
@@ -1483,16 +1511,16 @@
         </cx:title>
         <cx:tickLabels/>
         <cx:spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="CBD5E1"/>
             </a:solidFill>
           </a:ln>
         </cx:spPr>
         <cx:txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900">
                 <a:solidFill>
@@ -1510,8 +1538,8 @@
         <cx:title>
           <cx:tx>
             <cx:rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:r>
                   <a:rPr lang="en-US" sz="1100" b="1">
                     <a:solidFill>
@@ -1528,7 +1556,7 @@
         </cx:title>
         <cx:majorGridlines>
           <cx:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="E2E8F0"/>
               </a:solidFill>
@@ -1537,16 +1565,16 @@
         </cx:majorGridlines>
         <cx:tickLabels/>
         <cx:spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+          <a:ln w="12700">
             <a:solidFill>
               <a:srgbClr val="CBD5E1"/>
             </a:solidFill>
           </a:ln>
         </cx:spPr>
         <cx:txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900">
                 <a:solidFill>
@@ -1560,10 +1588,10 @@
         </cx:txPr>
       </cx:axis>
       <cx:spPr>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:solidFill>
           <a:srgbClr val="F8FAFC"/>
         </a:solidFill>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+        <a:ln w="9525">
           <a:solidFill>
             <a:srgbClr val="E2E8F0"/>
           </a:solidFill>
@@ -1572,9 +1600,9 @@
     </cx:plotArea>
     <cx:legend pos="t" align="ctr" overlay="0">
       <cx:txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000">
               <a:solidFill>
@@ -1589,10 +1617,10 @@
     </cx:legend>
   </cx:chart>
   <cx:spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+    <a:ln w="9525">
       <a:solidFill>
         <a:srgbClr val="CBD5E1"/>
       </a:solidFill>
@@ -6043,14 +6071,376 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90d27e1b566e48f6"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="B1" t="str">
+        <x:v>GroupA</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>GroupB</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Sales</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="B2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="B3" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="B4" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="B5" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="B8" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="B9" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="B10" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="B11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="B12" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="B13" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="B14" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="B15" t="n">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="B16" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="B17" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="B18" t="n">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6146797655084aa7"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4ca658c5f56466c"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="B1" t="str">
+        <x:v>US-East</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>EU-West</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>AP-South</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="B2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="B3" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="B4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="B5" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="B8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="B9" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="B10" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="B11" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="B12" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="B13" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="B14" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="B15" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="B16" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="B17" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="B18" t="n">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd1ad934e2d42a4"/>
 </x:worksheet>
 </file>